--- a/data/Class.xlsx
+++ b/data/Class.xlsx
@@ -463,9 +463,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="E5" t="inlineStr">
         <is>
@@ -490,13 +487,13 @@
         <v>500</v>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G6" t="n">
         <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -505,7 +502,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +522,13 @@
         <v>500</v>
       </c>
       <c r="F7" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -560,13 +557,13 @@
         <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I8" t="n">
         <v>5</v>
@@ -575,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
@@ -595,13 +592,13 @@
         <v>500</v>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -610,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -630,13 +627,13 @@
         <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -645,7 +642,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -665,13 +662,13 @@
         <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -680,7 +677,7 @@
         <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +697,13 @@
         <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G12" t="n">
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I12" t="n">
         <v>5</v>
@@ -715,7 +712,7 @@
         <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -735,13 +732,13 @@
         <v>500</v>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G13" t="n">
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
@@ -750,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -770,13 +767,13 @@
         <v>500</v>
       </c>
       <c r="F14" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="I14" t="n">
         <v>5</v>
@@ -785,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
